--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,21 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>initialFragmentId</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>maxStomachWidth</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>maxStomachHeight</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>startItems</t>
         </is>
       </c>
@@ -485,6 +500,21 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
@@ -519,6 +549,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>gut_4x4</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>item_big_plate</t>
         </is>
       </c>
@@ -552,6 +593,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>gut_4x4</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>item_chef_knife</t>
         </is>
       </c>
@@ -584,6 +636,17 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>gut_4x4</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,96 +471,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t>##comment</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>配置ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>角色名称</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>角色描述</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>角色立绘资源路径</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>初始菜谱ID</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>初始胃碎片ID</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>胃最大宽度</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>胃最大高度</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>list,string</t>
+          <t>初始携带道具ID列表</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>glutton_dog</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>大胃汪</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>暴食流。胃口越大，桌上的菜越不够看。</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sprites/Characters/char_glutton_dog</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>recipe_glutton</t>
+          <t>string</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>gut_4x4</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4</v>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>item_big_plate</t>
+          <t>list,string</t>
         </is>
       </c>
     </row>
@@ -568,27 +576,27 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>wok_cat</t>
+          <t>glutton_dog</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>铁锅喵</t>
+          <t>大胃汪</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>料理流。一手颠勺，一手挥刀，火候即是胜负。</t>
+          <t>暴食流。胃口越大，桌上的菜越不够看。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sprites/Characters/char_wok_cat</t>
+          <t>Sprites/Characters/char_glutton_dog</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>recipe_wok</t>
+          <t>recipe_glutton</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -604,7 +612,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>item_chef_knife</t>
+          <t>item_big_plate</t>
         </is>
       </c>
     </row>
@@ -612,27 +620,27 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chili_rat</t>
+          <t>wok_cat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>辣魔鼠</t>
+          <t>铁锅喵</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>火辣流。越吃越上头，辣到对手举旗投降。</t>
+          <t>料理流。一手颠勺，一手挥刀，火候即是胜负。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sprites/Characters/char_chili_rat</t>
+          <t>Sprites/Characters/char_wok_cat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>recipe_chili</t>
+          <t>recipe_wok</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -647,6 +655,50 @@
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>item_chef_knife</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>chili_rat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>辣魔鼠</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>火辣流。越吃越上头，辣到对手举旗投降。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sprites/Characters/char_chili_rat</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>recipe_chili</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>gut_4x4</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,16 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>timelinePool</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>bossPool</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>startItems</t>
         </is>
       </c>
@@ -516,6 +526,16 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>可用行动轴池，空=全部，逗号分隔 timeline.id</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>可用Boss池，空=全部，逗号分隔 boss.id</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>初始携带道具ID列表</t>
         </is>
       </c>
@@ -567,6 +587,16 @@
         </is>
       </c>
       <c r="J3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
@@ -612,6 +642,16 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>tl_normal,tl_boss</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>boss_glutton,boss_final</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>item_big_plate</t>
         </is>
       </c>
@@ -656,6 +696,16 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>tl_busy,tl_boss</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>boss_iron,boss_final</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>item_chef_knife</t>
         </is>
       </c>
@@ -698,7 +748,7 @@
       <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
@@ -1118,6 +1118,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>initialInterestCap</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>startItems</t>
         </is>
       </c>
@@ -1185,6 +1190,11 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>利息节点单次最高可获得金币数</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>初始携带道具ID列表</t>
         </is>
       </c>
@@ -1252,12 +1262,16 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>list,string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>glutton_dog</t>
@@ -1307,14 +1321,16 @@
       <c r="L4" t="n">
         <v>9999</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>item_big_plate</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>wok_cat</t>
@@ -1364,14 +1380,16 @@
       <c r="L5" t="n">
         <v>9999</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>item_chef_knife</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>chili_rat</t>
@@ -1411,7 +1429,10 @@
       <c r="L6" t="n">
         <v>9999</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -16,14 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -478,149 +471,149 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1038,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
@@ -1051,8 +1044,8 @@
     <col width="19.5384615384615" customWidth="1" min="8" max="8"/>
     <col width="20.1538461538462" customWidth="1" min="9" max="9"/>
     <col width="49.7692307692308" customWidth="1" min="10" max="10"/>
-    <col width="43" customWidth="1" min="11" max="11"/>
-    <col width="22.7692307692308" customWidth="1" min="12" max="12"/>
+    <col width="22.7692307692308" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,21 +1101,6 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>bossPool</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>initialGold</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>initialInterestCap</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>startItems</t>
         </is>
       </c>
@@ -1180,21 +1158,6 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>可用Boss池，空=全部，逗号分隔 boss.id</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>初始金币</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>利息节点单次最高可获得金币数</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>初始携带道具ID列表</t>
         </is>
       </c>
@@ -1252,21 +1215,6 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>list,string</t>
         </is>
       </c>
@@ -1315,17 +1263,6 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>boss_glutton,boss_final</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>item_big_plate</t>
         </is>
       </c>
@@ -1374,17 +1311,6 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>boss_iron,boss_final</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>item_chef_knife</t>
         </is>
       </c>
@@ -1426,13 +1352,7 @@
       <c r="I6" t="n">
         <v>8</v>
       </c>
-      <c r="L6" t="n">
-        <v>9999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>item_pepper_jar</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>tl_normal,tl_boss</t>
+          <t>tl_normal</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>tl_busy,tl_boss</t>
+          <t>tl_busy</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -4,25 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="character" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -125,7 +112,7 @@
     <t>recipe_glutton</t>
   </si>
   <si>
-    <t>gut_4x4</t>
+    <t>gut_3x4</t>
   </si>
   <si>
     <t>tl_normal</t>
@@ -176,7 +163,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="character" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
     <t>recipe_glutton</t>
   </si>
   <si>
-    <t>gut_3x4</t>
+    <t>gut_3x3</t>
   </si>
   <si>
     <t>tl_normal</t>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="character" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
     <t>recipe_glutton</t>
   </si>
   <si>
-    <t>gut_3x3</t>
+    <t>gut_4x3</t>
   </si>
   <si>
     <t>tl_normal</t>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="character" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -112,7 +125,7 @@
     <t>recipe_glutton</t>
   </si>
   <si>
-    <t>gut_4x3</t>
+    <t>gut_4x4</t>
   </si>
   <si>
     <t>tl_normal</t>
@@ -163,7 +176,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -4,30 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="character" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -68,10 +55,10 @@
     <t>配置ID</t>
   </si>
   <si>
-    <t>角色名称</t>
-  </si>
-  <si>
-    <t>角色描述</t>
+    <t>营业方向</t>
+  </si>
+  <si>
+    <t>方向描述</t>
   </si>
   <si>
     <t>角色立绘资源路径</t>
@@ -113,10 +100,11 @@
     <t>glutton_dog</t>
   </si>
   <si>
-    <t>甜品小熊</t>
-  </si>
-  <si>
-    <t>爱吃甜品的小熊</t>
+    <t>甜品</t>
+  </si>
+  <si>
+    <t>糖霜、奶油与烘焙香气打造的甜蜜世界
+众多精致甜品，让甜蜜在餐桌间不断传递，共享蛋糕盛宴</t>
   </si>
   <si>
     <t>Sprites/Characters/char_glutton_dog</t>
@@ -129,54 +117,12 @@
   </si>
   <si>
     <t>tl_normal</t>
-  </si>
-  <si>
-    <t>item_big_plate</t>
-  </si>
-  <si>
-    <t>wok_cat</t>
-  </si>
-  <si>
-    <t>铁锅喵</t>
-  </si>
-  <si>
-    <t>料理流。一手颠勺，一手挥刀，火候即是胜负。</t>
-  </si>
-  <si>
-    <t>Sprites/Characters/char_wok_cat</t>
-  </si>
-  <si>
-    <t>recipe_wok</t>
-  </si>
-  <si>
-    <t>tl_busy</t>
-  </si>
-  <si>
-    <t>item_chef_knife</t>
-  </si>
-  <si>
-    <t>chili_rat</t>
-  </si>
-  <si>
-    <t>辣魔鼠</t>
-  </si>
-  <si>
-    <t>火辣流。越吃越上头，辣到对手举旗投降。</t>
-  </si>
-  <si>
-    <t>Sprites/Characters/char_chili_rat</t>
-  </si>
-  <si>
-    <t>recipe_chili</t>
-  </si>
-  <si>
-    <t>item_pepper_jar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -784,8 +730,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1132,13 +1081,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="12.5384615384615" customWidth="1"/>
     <col min="3" max="3" width="10.3076923076923" customWidth="1"/>
-    <col min="4" max="4" width="51.5384615384615" customWidth="1"/>
+    <col min="4" max="4" width="148.461538461538" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="15.3846153846154" customWidth="1"/>
     <col min="7" max="7" width="18.3846153846154" customWidth="1"/>
@@ -1254,14 +1203,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" ht="34" spans="2:10">
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E4" t="s">
@@ -1274,77 +1223,13 @@
         <v>32</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
         <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="K6" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character" sheetId="1" r:id="Raa0e118c3f21477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character" sheetId="1" r:id="R059d7f0ddde742a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,12 +52,6 @@
     <x:t xml:space="preserve">方向描述</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">角色立绘资源路径</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">初始菜谱ID</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">初始胃碎片ID</x:t>
   </x:si>
   <x:si>
@@ -67,9 +61,6 @@
     <x:t xml:space="preserve">胃最大高度</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">初始携带道具ID列表</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">##type</x:t>
   </x:si>
   <x:si>
@@ -89,10 +80,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">甜品</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">糖霜、奶油与烘焙香气打造的甜蜜世界
-众多精致甜品，让甜蜜在餐桌间不断传递，共享蛋糕盛宴</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Sprites/Characters/char_glutton_dog</x:t>
@@ -953,77 +940,78 @@
       <x:c r="D2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E2" t="s">
+      <x:c r="E2" t="str">
+        <x:v>经营方向立绘资源路径</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>初始食谱ID</x:v>
+      </x:c>
+      <x:c r="G2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F2" t="s">
+      <x:c r="H2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G2" t="s">
+      <x:c r="I2" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="J2" t="s">
-        <x:v>19</x:v>
+      <x:c r="J2" t="str">
+        <x:v>初始携带装饰品和消耗品ID列表</x:v>
       </x:c>
       <x:c r="K2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B3" t="s">
+      <x:c r="I3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J3" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="C3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="H3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="J3" t="s">
-        <x:v>24</x:v>
       </x:c>
       <x:c r="K3"/>
     </x:row>
     <x:row r="4" ht="34">
       <x:c r="B4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>糖霜、奶油与烘焙香气打造的甜蜜世界
+众多精致甜品，让甜蜜在餐桌间不断传递，共享蛋糕星级评鉴</x:v>
+      </x:c>
+      <x:c r="E4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C4" t="s">
+      <x:c r="G4" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G4" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="H4">
         <x:v>12</x:v>

--- a/GourmetProject/GameConfig/Datas/character.xlsx
+++ b/GourmetProject/GameConfig/Datas/character.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character" sheetId="1" r:id="R059d7f0ddde742a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="character" sheetId="1" r:id="R475ba7f8890c4175"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1001,8 +1001,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="D4" s="1" t="str">
-        <x:v>糖霜、奶油与烘焙香气打造的甜蜜世界
-众多精致甜品，让甜蜜在餐桌间不断传递，共享蛋糕星级评鉴</x:v>
+        <x:v>糖霜、奶油与烘焙香气打造的甜蜜世界</x:v>
       </x:c>
       <x:c r="E4" t="s">
         <x:v>24</x:v>
